--- a/docs/원룸만들기_상품상세정보_답변_S0000DUB.xlsx
+++ b/docs/원룸만들기_상품상세정보_답변_S0000DUB.xlsx
@@ -908,7 +908,8 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>무타공 벽걸이 마운트와 스타일링 노즐은 현재 별도판매 품목이 아닙니다.</t>
+          <t>무타공 벽걸이 마운트와 스타일링 노즐은 현재 별도판매 품목이 아닙니다.
+뒷면 마그네틱 필터는 교체형 소모품이 아닙니다. 자석식이라 손으로 떼어내 먼지를 털어 반복 사용하는 부품이며, 별도 판매하지 않습니다.</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -1247,7 +1248,8 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>현재 고장으로 인한 A/S 외에 부속품을 교환은 불가능합니다.</t>
+          <t>현재 고장으로 인한 A/S 외에 부속품 교환은 불가능합니다.
+뒷면 마그네틱 필터는 교체형 소모품이 아니라 먼지를 털어 반복 사용하는 부품이라 교체 부품 목록에 포함되지 않습니다.</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
@@ -1375,7 +1377,9 @@
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>작동소음은 78dB입니다.</t>
+          <t>작동 소음은 78dB입니다. 드라이기 특성상 조용한 편은 아닙니다. (참고: 일반 대화가 약 60dB, 진공청소기가 70~80dB 수준입니다.)
+원룸이나 심야에 사용하실 때는 1단으로 쓰시면 풍속이 낮아지면서 소음도 함께 줄어듭니다.
+벽 거치 구조라 사용 후 서랍을 여닫을 일이 없어, 심야에는 그만큼 소리가 덜 납니다.</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">

--- a/docs/원룸만들기_상품상세정보_답변_S0000DUB.xlsx
+++ b/docs/원룸만들기_상품상세정보_답변_S0000DUB.xlsx
@@ -877,7 +877,7 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>78dB</t>
+          <t>78dB (2단 기준)</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>내용 확인을 위한 포장 개봉만으로 반품이 제한되지는 않습니다. 다만 포장 박스가 훼손되거나, 보호필름이 떨어진 경우와 고객 책임으로 제품이 훼손되거나 사용 및 일부 소비로 가치가 크게 감소한 경우에는 반품이 제한될 수 있습니다.</t>
+          <t>내용 확인을 위한 포장 개봉만으로 반품이 제한되지는 않습니다. 다만 고객 책임으로 제품이 훼손되거나 사용 및 일부 소비로 가치가 크게 감소한 경우에는 반품이 제한될 수 있습니다.</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -1147,7 +1147,10 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>포장 개봉만으로 감가하지 않습니다. 고객 책임으로 상품 가치가 실제로 감소한 경우에만 사전 고지된 기준을 적용할 수 있으며, 포장재 훼손 및 구성품 파손 등은 감가 공제가 아니라 전체 금액을 부담하여야 합니다. 재판매가 어렵습니다.</t>
+          <t>포장을 열어 내용을 확인한 것만으로는 감가하거나 반품을 제한하지 않습니다.
+반품이 제한되는 경우는 소비자 책임으로 제품이 멸실·훼손되었거나, 사용 또는 일부 소비로 제품 가치가 현저히 감소한 경우입니다. 이에 해당하는지는 넬리아가 사진 등으로 확인한 뒤 고객께 안내드립니다.
+포장재의 통상적인 개봉 흔적은 반품 제한 사유나 감가 사유로 적용하지 않습니다.
+별도의 감가 공제율은 운영하지 않으며, 단순 변심 반품의 경우 반송비(편도 3,000원 / 왕복 6,000원, 도서산간 5,000원 추가)만 고객이 부담합니다.</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
@@ -1377,7 +1380,7 @@
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>작동 소음은 78dB입니다. 드라이기 특성상 조용한 편은 아닙니다. (참고: 일반 대화가 약 60dB, 진공청소기가 70~80dB 수준입니다.)
+          <t>작동 소음은 2단(최대) 기준 78dB입니다. 드라이기 특성상 조용한 편은 아닙니다. (참고: 일반 대화가 약 60dB, 진공청소기가 70~80dB 수준입니다.)
 원룸이나 심야에 사용하실 때는 1단으로 쓰시면 풍속이 낮아지면서 소음도 함께 줄어듭니다.
 벽 거치 구조라 사용 후 서랍을 여닫을 일이 없어, 심야에는 그만큼 소리가 덜 납니다.</t>
         </is>

--- a/docs/원룸만들기_상품상세정보_답변_S0000DUB.xlsx
+++ b/docs/원룸만들기_상품상세정보_답변_S0000DUB.xlsx
@@ -1421,7 +1421,7 @@
 [무상] 정상 사용 중 전원 불량, 모터 이상, 과열 차단 반복, 풍량·온도 조절 불량, 조립 불량, 외부 손상이 없는 코드 단선.
 [유상] 낙하·침수·충격에 의한 파손, 분해 흔적이 있는 경우, 정격 외 전압 사용, 소모품 분실·파손, 보증 기간 경과.
 [처리 방식] 제품 구조상 부품 단위 수리를 하지 않고 교환으로 처리합니다. 보증 기간 내 하자는 신품 교환이며 왕복 배송비는 넬리아가 부담합니다. 과실 파손과 보증 기간 경과 건은 유상 교환입니다.
-[유상 교환 비용] ○○○원 + 왕복 배송비 6,000원 (도서산간 5,000원 추가)
+[유상 교환 비용] 접수 시 개별 안내드립니다. 제품 상태를 확인한 뒤 비용을 먼저 알려 드리며, 고객 동의 없이 진행하지 않습니다. 왕복 배송비 6,000원(도서산간 5,000원 추가)은 고객 부담입니다.
 [반복 하자] 동일 하자로 2회 교환 후 재발하면 환불해 드립니다.
 [처리 기간] 접수 후 영업일 기준 7일 이내 교환품을 발송합니다.
 [접수] 070-8983-7692 / twolee@nellialab.com</t>
